--- a/web/files/九龙-九龙塘-The Monet 第1期.xlsx
+++ b/web/files/九龙-九龙塘-The Monet 第1期.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -711,17 +710,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -783,17 +782,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -855,17 +854,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -927,17 +926,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -999,12 +998,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1071,12 +1070,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1143,17 +1142,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1215,17 +1214,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1287,17 +1286,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1359,17 +1358,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1431,12 +1430,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1503,12 +1502,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1575,17 +1574,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1647,17 +1646,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1719,17 +1718,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1791,17 +1790,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1863,12 +1862,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1935,12 +1934,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2007,17 +2006,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2079,17 +2078,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2151,17 +2150,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2223,17 +2222,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2295,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2367,12 +2366,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2439,17 +2438,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -2511,17 +2510,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2583,17 +2582,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -2655,17 +2654,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2732,12 +2731,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2804,12 +2803,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2876,12 +2875,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2948,12 +2947,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3020,12 +3019,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -3092,12 +3091,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3164,12 +3163,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3236,12 +3235,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3308,12 +3307,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3380,12 +3379,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3452,12 +3451,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3524,12 +3523,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3596,12 +3595,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3668,12 +3667,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3740,12 +3739,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3812,12 +3811,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3884,12 +3883,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3943,2022 +3942,6 @@
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N71" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>null房</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5974,439 +3957,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 0呎 (null房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
